--- a/Data/Nhaptiendo.xlsx
+++ b/Data/Nhaptiendo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tuyenmt\Downloads\prj_warehouse_bivn-soft\prj_warehouse_bivn-soft\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42962F26-D3E8-4B2D-B60F-BC2883F2613E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1573D00-2795-4A8E-BBDA-EE54B2BD5EE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{928DFE57-C616-4DC4-9C76-64E7CA44C9B1}"/>
+    <workbookView xWindow="7770" yWindow="-14970" windowWidth="26640" windowHeight="14370" xr2:uid="{928DFE57-C616-4DC4-9C76-64E7CA44C9B1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -99,11 +99,11 @@
 (Năm-Tháng-Ngày)</t>
   </si>
   <si>
-    <t>Ngày NCC giao
+    <t>Ngày GH thực tế
 (Năm-Tháng-Ngày)</t>
   </si>
   <si>
-    <t>Ngày GH thực tế
+    <t>Ngày GH Dự kiến
 (Năm-Tháng-Ngày)</t>
   </si>
 </sst>
@@ -660,10 +660,10 @@
         <v>9</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="O1" s="12" t="s">
         <v>10</v>
